--- a/data/WBS_Tutor_Inteligente_ITM.xlsx
+++ b/data/WBS_Tutor_Inteligente_ITM.xlsx
@@ -69,7 +69,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +84,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2433"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F46B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECEAFB"/>
       </patternFill>
     </fill>
     <fill>
@@ -153,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -228,6 +238,18 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -598,13 +620,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="82" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -617,7 +639,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estructura de Desglose del Trabajo del MVP · ITM — Esp. en Ingeniería de Software · Gestión de Proyectos · Descompuesto hasta Nivel 3</t>
+          <t>Estructura de Desglose del Trabajo del MVP · Incluye Gestión del Proyecto · Descompuesto hasta Nivel 3</t>
         </is>
       </c>
     </row>
@@ -670,12 +692,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Requisitos y análisis</t>
+          <t>Gestión del Proyecto</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
@@ -690,12 +712,12 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Elicitación de requisitos</t>
+          <t>Inicio y planificación</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
@@ -710,12 +732,12 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Instrumentos de encuesta (docentes y estudiantes)</t>
+          <t>Acta de constitución / definición de alcance (MVP)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
@@ -730,59 +752,59 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Análisis del problema y necesidades</t>
+          <t>Cronograma y plan de releases (MVP / R2 / R3)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Requisitos funcionales (RF)</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Requisitos</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>1.1.3</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Product Backlog inicial y estimación (story points)</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Historias de usuario y backlog priorizado</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Requisitos</t>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>1.1.4</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Plan de gestión de riesgos</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
@@ -790,19 +812,19 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Requisitos no funcionales (ISO/IEC 25010)</t>
+          <t>Ejecución y seguimiento ágil (Scrum)</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>1.4.1</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
@@ -810,19 +832,19 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Catálogo de RNF (14 requisitos)</t>
+          <t>Sprint planning</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>1.4.2</t>
+          <t>1.2.2</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
@@ -830,159 +852,159 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Priorización de atributos de calidad (pesos 0–5)</t>
+          <t>Daily standups</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Criterios de aceptación</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Requisitos</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Diseño</t>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>1.2.3</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Gestión del tablero en Azure DevOps</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>1.2.4</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Sprint review / demo</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Arquitectura de la solución</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>Diseño</t>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>1.2.5</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Retrospectiva</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>2.1.1</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Diagrama de arquitectura de alto nivel (4 módulos · SPA + API REST · API + worker · CQRS/colas)</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Diseño</t>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Monitoreo y control</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Decisiones arquitectónicas (ADR) y stack</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>Diseño</t>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>1.3.1</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Seguimiento de avance (burndown / velocity)</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Modelo de datos</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>Diseño</t>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>1.3.2</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Control de cambios</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Diseño del modelo evaluativo y rúbricas</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>Diseño</t>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>1.3.3</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Seguimiento de riesgos e impedimentos</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>1.3.4</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
@@ -990,39 +1012,39 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Rúbricas y contexto de evaluación (contexto, resp. correcta/incorrecta, palabras clave, resp. del estudiante)</t>
+          <t>Aseguramiento de calidad del proceso (DoD)</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Diseño</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>2.4.2</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Criterios de clasificación por niveles (LLM juez)</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Diseño</t>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Gestión académica del trabajo de grado</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>2.4.3</t>
+          <t>1.4.1</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
@@ -1030,99 +1052,99 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>Algoritmo de selección de rutas</t>
+          <t>Entregables de seminario</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Diseño</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Mockups de baja fidelidad</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>1.4.2</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Documento de trabajo de grado</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>1.4.3</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Reuniones con asesor / director</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>Módulo Gestión de Usuarios</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>1.4.4</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Preparación de la sustentación</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>3.1.1</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Backend (auth, RBAC, MFA-OTP)</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>3.1.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
@@ -1130,39 +1152,39 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Frontend (registro, login, perfil)</t>
+          <t>Aceptación del MVP y lecciones aprendidas</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Desarrollo</t>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>Módulo Evaluación de Conocimientos</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>1.5.2</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Entrega final y archivo del proyecto</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>1. Gestión del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>3.2.1</t>
+          <t>1.5.3</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
@@ -1170,79 +1192,79 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Backend (cuestionarios, autosave)</t>
+          <t>Retrospectiva global del proyecto</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Desarrollo</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>3.2.2</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>Evaluación con LLM juez (envío de contexto + rúbrica)</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+          <t>1. Gestión del Proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Requisitos y análisis</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>2. Requisitos y análisis</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>3.2.3</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Frontend (vista de evaluación)</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Elicitación de requisitos</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>2. Requisitos y análisis</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>Módulo Clasificación y Diagnóstico</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>2.1.1</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Instrumentos de encuesta (docentes y estudiantes)</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>2. Requisitos y análisis</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>3.3.1</t>
+          <t>2.1.2</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
@@ -1250,79 +1272,79 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Lógica de clasificación por niveles (a partir del LLM juez)</t>
+          <t>Análisis del problema y necesidades</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Desarrollo</t>
+          <t>2. Requisitos y análisis</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>3.3.2</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>Servicio de clasificación e historial de evolución</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Requisitos funcionales (RF)</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>2. Requisitos y análisis</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>Módulo Recomendación de Rutas de Aprendizaje</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Historias de usuario y backlog priorizado</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>2. Requisitos y análisis</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>3.4.1</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>Backend (asignación de rutas, recursos)</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Requisitos no funcionales (ISO/IEC 25010)</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>2. Requisitos y análisis</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
@@ -1330,99 +1352,99 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>Frontend (vistas de ruta, progreso, retroalimentación)</t>
+          <t>Catálogo de RNF (14 requisitos)</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Desarrollo</t>
+          <t>2. Requisitos y análisis</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" s="20" t="inlineStr">
-        <is>
-          <t>Infraestructura y componentes transversales</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Priorización de atributos de calidad (pesos 0–5)</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>2. Requisitos y análisis</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>3.5.1</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>API REST y configuración de entorno</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>3.5.2</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
-        <is>
-          <t>Worker de mensajería (colas durables, reintentos)</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Criterios de aceptación</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>2. Requisitos y análisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>3. Diseño</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>3.5.3</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C43" s="13" t="inlineStr">
-        <is>
-          <t>Worker de LLM</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>Arquitectura de la solución</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>3. Diseño</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>3.5.4</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="B44" s="12" t="n">
@@ -1430,199 +1452,199 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>Audit trail / trazabilidad</t>
+          <t>Diagrama de arquitectura de alto nivel (4 módulos · SPA + API REST · API + worker · CQRS/colas)</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
+          <t>3. Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>Decisiones arquitectónicas (ADR) y stack</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t>3. Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>Modelo de datos</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>3. Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>Diseño del modelo evaluativo y rúbricas</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t>3. Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>3.4.1</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Rúbricas y contexto de evaluación (contexto, resp. correcta/incorrecta, palabras clave, resp. del estudiante)</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>3. Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>3.4.2</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>Criterios de clasificación por niveles (LLM juez)</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>3. Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>3.4.3</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Algoritmo de selección de rutas</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>3. Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>Mockups de baja fidelidad</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t>3. Diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
           <t>Desarrollo</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>3.5.5</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>Failover del proveedor LLM</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>Desarrollo</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B46" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="22" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-      <c r="D46" s="23" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B47" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>Pruebas unitarias</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="24" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>Pruebas de integración</t>
-        </is>
-      </c>
-      <c r="D48" s="25" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>Pruebas funcionales (validación de HU)</t>
-        </is>
-      </c>
-      <c r="D49" s="25" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="B50" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>Pruebas no funcionales</t>
-        </is>
-      </c>
-      <c r="D50" s="25" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>4.4.1</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>Seguridad (NFR-01, 02, 03, 10)</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>4.4.2</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>Fiabilidad: tolerancia a fallos y recuperación (NFR-04, 05, 06, 13, 14)</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>4.4.3</t>
-        </is>
-      </c>
-      <c r="B53" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>Disponibilidad (NFR-11, 12)</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
+      <c r="B53" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>Módulo Gestión de Usuarios</t>
+        </is>
+      </c>
+      <c r="D53" s="25" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>4.4.4</t>
+          <t>4.1.1</t>
         </is>
       </c>
       <c r="B54" s="12" t="n">
@@ -1630,39 +1652,39 @@
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>Rendimiento / carga</t>
+          <t>Backend (auth, RBAC, MFA-OTP)</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>4. Desarrollo</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="B55" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" s="24" t="inlineStr">
-        <is>
-          <t>Pruebas de aceptación (UAT con docentes)</t>
-        </is>
-      </c>
-      <c r="D55" s="25" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>4.1.2</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Frontend (registro, login, perfil)</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="B56" s="25" t="n">
@@ -1670,27 +1692,547 @@
       </c>
       <c r="C56" s="24" t="inlineStr">
         <is>
+          <t>Módulo Evaluación de Conocimientos</t>
+        </is>
+      </c>
+      <c r="D56" s="25" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>4.2.1</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>Backend (cuestionarios, autosave)</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>4.2.2</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>Evaluación con LLM juez (envío de contexto + rúbrica)</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>4.2.3</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>Frontend (vista de evaluación)</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B60" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>Módulo Clasificación y Diagnóstico</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Lógica de clasificación por niveles (a partir del LLM juez)</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>4.3.2</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>Servicio de clasificación e historial de evolución</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>Módulo Recomendación de Rutas de Aprendizaje</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>4.4.1</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>Backend (asignación de rutas, recursos)</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>4.4.2</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>Frontend (vistas de ruta, progreso, retroalimentación)</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>Infraestructura y componentes transversales</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>4.5.1</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>API REST y configuración de entorno</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>4.5.2</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Worker de mensajería (colas durables, reintentos)</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>4.5.3</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Worker de LLM</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>4.5.4</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Audit trail / trazabilidad</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>4.5.5</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>Failover del proveedor LLM</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>4. Desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B72" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="D72" s="27" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B73" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>Pruebas unitarias</t>
+        </is>
+      </c>
+      <c r="D73" s="29" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B74" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>Pruebas de integración</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="B75" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>Pruebas funcionales (validación de HU)</t>
+        </is>
+      </c>
+      <c r="D75" s="29" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="28" t="inlineStr">
+        <is>
+          <t>Pruebas no funcionales</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>5.4.1</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>Seguridad (NFR-01, 02, 03, 10)</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>5.4.2</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>Fiabilidad: tolerancia a fallos y recuperación (NFR-04, 05, 06, 13, 14)</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>5.4.3</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>Disponibilidad (NFR-11, 12)</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>5.4.4</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Rendimiento / carga</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="28" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="B81" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="28" t="inlineStr">
+        <is>
+          <t>Pruebas de aceptación (UAT con docentes)</t>
+        </is>
+      </c>
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="B82" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
           <t>Corrección de defectos</t>
         </is>
       </c>
-      <c r="D56" s="25" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="26" t="inlineStr">
-        <is>
-          <t>Regla del 100 %: los 4 entregables principales cubren todo el trabajo del MVP; cada elemento pertenece a un solo padre. Profundidad máxima = Nivel 3 (paquetes de trabajo).</t>
+      <c r="D82" s="29" t="inlineStr">
+        <is>
+          <t>5. Pruebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
+          <t>Regla del 100 %: los 5 entregables principales cubren todo el trabajo del proyecto. Gestión del Proyecto es transversal (dirección, seguimiento y cierre); el aseguramiento de calidad del producto vive en la rama Pruebas.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A84:D84"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A58:D58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>

--- a/data/WBS_Tutor_Inteligente_ITM.xlsx
+++ b/data/WBS_Tutor_Inteligente_ITM.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D58"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" customWidth="1"/>
@@ -455,7 +455,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="str">
-        <v>Inicio y planificación</v>
+        <v>Creación de acta de constitución del proyecto</v>
       </c>
       <c r="D4" t="str">
         <v>1. Gestión del Proyecto</v>
@@ -463,13 +463,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1.1.1</v>
+        <v>1.2</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="str">
-        <v>Acta de constitución / definición de alcance (MVP)</v>
+        <v>Desarrollar cronograma</v>
       </c>
       <c r="D5" t="str">
         <v>1. Gestión del Proyecto</v>
@@ -477,13 +477,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>1.1.2</v>
+        <v>1.3</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="str">
-        <v>Cronograma y plan de releases (MVP / R2 / R3)</v>
+        <v>Gestión de riesgos</v>
       </c>
       <c r="D6" t="str">
         <v>1. Gestión del Proyecto</v>
@@ -491,13 +491,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1.1.3</v>
+        <v>1.4</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>Product Backlog inicial y estimación (story points)</v>
+        <v>Monitoreo de progreso</v>
       </c>
       <c r="D7" t="str">
         <v>1. Gestión del Proyecto</v>
@@ -505,1057 +505,721 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1.1.4</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="str">
-        <v>Plan de gestión de riesgos</v>
+        <v>Requisitos y análisis</v>
       </c>
       <c r="D8" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="str">
-        <v>Ejecución y seguimiento ágil (Scrum)</v>
+        <v>Elicitación de requisitos</v>
       </c>
       <c r="D9" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1.2.1</v>
+        <v>2.1.1</v>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10" t="str">
-        <v>Sprint planning</v>
+        <v>Instrumentos de encuesta (docentes y estudiantes)</v>
       </c>
       <c r="D10" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1.2.2</v>
+        <v>2.1.2</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
       <c r="C11" t="str">
-        <v>Daily standups</v>
+        <v>Análisis del problema y necesidades</v>
       </c>
       <c r="D11" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1.2.3</v>
+        <v>2.2</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="str">
-        <v>Gestión del tablero en Azure DevOps</v>
+        <v>Requisitos funcionales (RF)</v>
       </c>
       <c r="D12" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1.2.4</v>
+        <v>2.3</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="str">
-        <v>Sprint review / demo</v>
+        <v>Historias de usuario y backlog priorizado</v>
       </c>
       <c r="D13" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1.2.5</v>
+        <v>2.4</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="str">
-        <v>Retrospectiva</v>
+        <v>Requisitos no funcionales (ISO/IEC 25010)</v>
       </c>
       <c r="D14" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>1.3</v>
+        <v>2.4.1</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="str">
-        <v>Monitoreo y control</v>
+        <v>Catálogo de RNF (14 requisitos)</v>
       </c>
       <c r="D15" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1.3.1</v>
+        <v>2.4.2</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16" t="str">
-        <v>Seguimiento de avance (burndown / velocity)</v>
+        <v>Priorización de atributos de calidad (pesos 0–5)</v>
       </c>
       <c r="D16" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>1.3.2</v>
+        <v>2.5</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="str">
-        <v>Control de cambios</v>
+        <v>Criterios de aceptación</v>
       </c>
       <c r="D17" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>2. Requisitos y análisis</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1.3.3</v>
+        <v>3</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>Seguimiento de riesgos e impedimentos</v>
+        <v>Diseño</v>
       </c>
       <c r="D18" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1.3.4</v>
+        <v>3.1</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>Aseguramiento de calidad del proceso (DoD)</v>
+        <v>Arquitectura de la solución</v>
       </c>
       <c r="D19" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1.4</v>
+        <v>3.1.1</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>Gestión académica del trabajo de grado</v>
+        <v>Diagrama de arquitectura de alto nivel (4 módulos · SPA + API REST · API + worker · CQRS/colas)</v>
       </c>
       <c r="D20" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1.4.1</v>
+        <v>3.2</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" t="str">
-        <v>Entregables de seminario</v>
+        <v>Decisiones arquitectónicas (ADR) y stack</v>
       </c>
       <c r="D21" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1.4.2</v>
+        <v>3.3</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="str">
-        <v>Documento de trabajo de grado</v>
+        <v>Modelo de datos</v>
       </c>
       <c r="D22" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>1.4.3</v>
+        <v>3.4</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>Reuniones con asesor / director</v>
+        <v>Diseño del modelo evaluativo y rúbricas</v>
       </c>
       <c r="D23" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>1.4.4</v>
+        <v>3.4.1</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="str">
-        <v>Preparación de la sustentación</v>
+        <v>Rúbricas y contexto de evaluación (contexto, resp. correcta/incorrecta, palabras clave, resp. del estudiante)</v>
       </c>
       <c r="D24" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>1.5</v>
+        <v>3.4.2</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="str">
-        <v>Cierre</v>
+        <v>Criterios de clasificación por niveles (LLM juez)</v>
       </c>
       <c r="D25" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>1.5.1</v>
+        <v>3.4.3</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26" t="str">
-        <v>Aceptación del MVP y lecciones aprendidas</v>
+        <v>Algoritmo de selección de rutas</v>
       </c>
       <c r="D26" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>1.5.2</v>
+        <v>3.5</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="str">
-        <v>Entrega final y archivo del proyecto</v>
+        <v>Mockups de baja fidelidad</v>
       </c>
       <c r="D27" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>3. Diseño</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>1.5.3</v>
+        <v>4</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28" t="str">
-        <v>Retrospectiva global del proyecto</v>
+        <v>Desarrollo</v>
       </c>
       <c r="D28" t="str">
-        <v>1. Gestión del Proyecto</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="str">
-        <v>Requisitos y análisis</v>
+        <v>Módulo Gestión de Usuarios</v>
       </c>
       <c r="D29" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2.1</v>
+        <v>4.1.1</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="str">
-        <v>Elicitación de requisitos</v>
+        <v>Backend (auth, RBAC, MFA-OTP)</v>
       </c>
       <c r="D30" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2.1.1</v>
+        <v>4.1.2</v>
       </c>
       <c r="B31">
         <v>3</v>
       </c>
       <c r="C31" t="str">
-        <v>Instrumentos de encuesta (docentes y estudiantes)</v>
+        <v>Frontend (registro, login, perfil)</v>
       </c>
       <c r="D31" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2.1.2</v>
+        <v>4.2</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" t="str">
-        <v>Análisis del problema y necesidades</v>
+        <v>Módulo Evaluación de Conocimientos</v>
       </c>
       <c r="D32" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2.1.3</v>
+        <v>4.2.1</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33" t="str">
-        <v>Criterios de aceptación</v>
+        <v>Backend (cuestionarios, autosave)</v>
       </c>
       <c r="D33" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2.2</v>
+        <v>4.2.2</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="str">
-        <v>Requisitos funcionales (RF)</v>
+        <v>Evaluación con LLM juez (envío de contexto + rúbrica)</v>
       </c>
       <c r="D34" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2.3</v>
+        <v>4.2.3</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" t="str">
-        <v>Historias de usuario y backlog priorizado</v>
+        <v>Frontend (vista de evaluación)</v>
       </c>
       <c r="D35" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="str">
-        <v>Requisitos no funcionales (ISO/IEC 25010)</v>
+        <v>Módulo Clasificación y Diagnóstico</v>
       </c>
       <c r="D36" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2.4.1</v>
+        <v>4.3.1</v>
       </c>
       <c r="B37">
         <v>3</v>
       </c>
       <c r="C37" t="str">
-        <v>Catálogo de RNF (14 requisitos)</v>
+        <v>Lógica de clasificación por niveles (a partir del LLM juez)</v>
       </c>
       <c r="D37" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2.4.2</v>
+        <v>4.3.2</v>
       </c>
       <c r="B38">
         <v>3</v>
       </c>
       <c r="C38" t="str">
-        <v>Priorización de atributos de calidad (pesos 0–5)</v>
+        <v>Servicio de clasificación e historial de evolución</v>
       </c>
       <c r="D38" t="str">
-        <v>2. Requisitos y análisis</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="str">
-        <v>Diseño</v>
+        <v>Módulo Recomendación de Rutas de Aprendizaje</v>
       </c>
       <c r="D39" t="str">
-        <v>3. Diseño</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>3.1</v>
+        <v>4.4.1</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" t="str">
-        <v>Arquitectura de la solución</v>
+        <v>Backend (asignación de rutas, recursos)</v>
       </c>
       <c r="D40" t="str">
-        <v>3. Diseño</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>3.1.1</v>
+        <v>4.4.2</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41" t="str">
-        <v>Diagrama de arquitectura de alto nivel (4 módulos · SPA + API REST · API + worker · CQRS/colas)</v>
+        <v>Frontend (vistas de ruta, progreso, retroalimentación)</v>
       </c>
       <c r="D41" t="str">
-        <v>3. Diseño</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
       <c r="C42" t="str">
-        <v>Decisiones arquitectónicas (ADR) y stack</v>
+        <v>Infraestructura y componentes transversales</v>
       </c>
       <c r="D42" t="str">
-        <v>3. Diseño</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>3.2.1</v>
+        <v>4.5.1</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43" t="str">
-        <v>Tabla de ADR</v>
+        <v>API REST y configuración de entorno</v>
       </c>
       <c r="D43" t="str">
-        <v>3. Diseño</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>3.3</v>
+        <v>4.5.2</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="str">
-        <v>Modelo de datos</v>
+        <v>Worker de mensajería (colas durables, reintentos)</v>
       </c>
       <c r="D44" t="str">
-        <v>3. Diseño</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>3.3.1</v>
+        <v>4.5.3</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45" t="str">
-        <v xml:space="preserve">Esquema de datos </v>
+        <v>Worker de LLM</v>
       </c>
       <c r="D45" t="str">
-        <v>3. Diseño</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>3.4</v>
+        <v>4.5.4</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="str">
-        <v>Diseño del modelo evaluativo y rúbricas</v>
+        <v>Audit trail / trazabilidad</v>
       </c>
       <c r="D46" t="str">
-        <v>3. Diseño</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>3.4.1</v>
+        <v>4.5.5</v>
       </c>
       <c r="B47">
         <v>3</v>
       </c>
       <c r="C47" t="str">
-        <v>Rúbricas y contexto de evaluación (contexto, resp. correcta/incorrecta, palabras clave, resp. del estudiante)</v>
+        <v>Failover del proveedor LLM</v>
       </c>
       <c r="D47" t="str">
-        <v>3. Diseño</v>
+        <v>4. Desarrollo</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>3.4.2</v>
+        <v>5</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48" t="str">
-        <v>Criterios de clasificación por niveles (LLM juez)</v>
+        <v>Pruebas</v>
       </c>
       <c r="D48" t="str">
-        <v>3. Diseño</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>3.4.3</v>
+        <v>5.1</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" t="str">
-        <v>Algoritmo de selección de rutas</v>
+        <v>Pruebas unitarias</v>
       </c>
       <c r="D49" t="str">
-        <v>3. Diseño</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50" t="str">
-        <v>Mockups de baja fidelidad</v>
+        <v>Pruebas de integración</v>
       </c>
       <c r="D50" t="str">
-        <v>3. Diseño</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>3.5.1</v>
+        <v>5.3</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" t="str">
-        <v>Archivos Mockups</v>
+        <v>Pruebas funcionales (validación de HU)</v>
       </c>
       <c r="D51" t="str">
-        <v>3. Diseño</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="str">
-        <v>Desarrollo</v>
+        <v>Pruebas no funcionales</v>
       </c>
       <c r="D52" t="str">
-        <v>4. Desarrollo</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>4.1</v>
+        <v>5.4.1</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" t="str">
-        <v>Módulo Gestión de Usuarios</v>
+        <v>Seguridad (NFR-01, 02, 03, 10)</v>
       </c>
       <c r="D53" t="str">
-        <v>4. Desarrollo</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>4.1.1</v>
+        <v>5.4.2</v>
       </c>
       <c r="B54">
         <v>3</v>
       </c>
       <c r="C54" t="str">
-        <v>Backend (auth, RBAC, MFA-OTP)</v>
+        <v>Fiabilidad: tolerancia a fallos y recuperación (NFR-04, 05, 06, 13, 14)</v>
       </c>
       <c r="D54" t="str">
-        <v>4. Desarrollo</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>4.1.2</v>
+        <v>5.4.3</v>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55" t="str">
-        <v>Frontend (registro, login, perfil)</v>
+        <v>Disponibilidad (NFR-11, 12)</v>
       </c>
       <c r="D55" t="str">
-        <v>4. Desarrollo</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>4.2</v>
+        <v>5.4.4</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="str">
-        <v>Módulo Evaluación de Conocimientos</v>
+        <v>Rendimiento / carga</v>
       </c>
       <c r="D56" t="str">
-        <v>4. Desarrollo</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>4.2.1</v>
+        <v>5.5</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="str">
-        <v>Backend (cuestionarios, autosave)</v>
+        <v>Pruebas de aceptación (UAT con docentes)</v>
       </c>
       <c r="D57" t="str">
-        <v>4. Desarrollo</v>
+        <v>5. Pruebas</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>4.2.2</v>
+        <v>5.6</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" t="str">
-        <v>Evaluación con LLM juez (envío de contexto + rúbrica)</v>
+        <v>Corrección de defectos</v>
       </c>
       <c r="D58" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>4.2.3</v>
-      </c>
-      <c r="B59">
-        <v>3</v>
-      </c>
-      <c r="C59" t="str">
-        <v>Frontend (vista de evaluación)</v>
-      </c>
-      <c r="D59" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>4.3</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Módulo Clasificación y Diagnóstico</v>
-      </c>
-      <c r="D60" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>4.3.1</v>
-      </c>
-      <c r="B61">
-        <v>3</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Lógica de clasificación por niveles (a partir del LLM juez)</v>
-      </c>
-      <c r="D61" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>4.3.2</v>
-      </c>
-      <c r="B62">
-        <v>3</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Servicio de clasificación e historial de evolución</v>
-      </c>
-      <c r="D62" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>4.4</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Módulo Recomendación de Rutas de Aprendizaje</v>
-      </c>
-      <c r="D63" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>4.4.1</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Backend (asignación de rutas, recursos)</v>
-      </c>
-      <c r="D64" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>4.4.2</v>
-      </c>
-      <c r="B65">
-        <v>3</v>
-      </c>
-      <c r="C65" t="str">
-        <v>Frontend (vistas de ruta, progreso, retroalimentación)</v>
-      </c>
-      <c r="D65" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>4.5</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Infraestructura y componentes transversales</v>
-      </c>
-      <c r="D66" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>4.5.1</v>
-      </c>
-      <c r="B67">
-        <v>3</v>
-      </c>
-      <c r="C67" t="str">
-        <v>API REST y configuración de entorno</v>
-      </c>
-      <c r="D67" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>4.5.2</v>
-      </c>
-      <c r="B68">
-        <v>3</v>
-      </c>
-      <c r="C68" t="str">
-        <v>Worker de mensajería (colas durables, reintentos)</v>
-      </c>
-      <c r="D68" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>4.5.3</v>
-      </c>
-      <c r="B69">
-        <v>3</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Worker de LLM</v>
-      </c>
-      <c r="D69" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>4.5.4</v>
-      </c>
-      <c r="B70">
-        <v>3</v>
-      </c>
-      <c r="C70" t="str">
-        <v>Audit trail / trazabilidad</v>
-      </c>
-      <c r="D70" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>4.5.5</v>
-      </c>
-      <c r="B71">
-        <v>3</v>
-      </c>
-      <c r="C71" t="str">
-        <v>Failover del proveedor LLM</v>
-      </c>
-      <c r="D71" t="str">
-        <v>4. Desarrollo</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>5</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72" t="str">
-        <v>Pruebas</v>
-      </c>
-      <c r="D72" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>5.1</v>
-      </c>
-      <c r="B73">
-        <v>2</v>
-      </c>
-      <c r="C73" t="str">
-        <v>Pruebas unitarias</v>
-      </c>
-      <c r="D73" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>5.2</v>
-      </c>
-      <c r="B74">
-        <v>2</v>
-      </c>
-      <c r="C74" t="str">
-        <v>Pruebas de integración</v>
-      </c>
-      <c r="D74" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>5.3</v>
-      </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75" t="str">
-        <v>Pruebas funcionales (validación de HU)</v>
-      </c>
-      <c r="D75" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>5.4</v>
-      </c>
-      <c r="B76">
-        <v>2</v>
-      </c>
-      <c r="C76" t="str">
-        <v>Pruebas no funcionales</v>
-      </c>
-      <c r="D76" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>5.4.1</v>
-      </c>
-      <c r="B77">
-        <v>3</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Seguridad (NFR-01, 02, 03, 10)</v>
-      </c>
-      <c r="D77" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>5.4.2</v>
-      </c>
-      <c r="B78">
-        <v>3</v>
-      </c>
-      <c r="C78" t="str">
-        <v>Fiabilidad: tolerancia a fallos y recuperación (NFR-04, 05, 06, 13, 14)</v>
-      </c>
-      <c r="D78" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>5.4.3</v>
-      </c>
-      <c r="B79">
-        <v>3</v>
-      </c>
-      <c r="C79" t="str">
-        <v>Disponibilidad (NFR-11, 12)</v>
-      </c>
-      <c r="D79" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>5.4.4</v>
-      </c>
-      <c r="B80">
-        <v>3</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Rendimiento / carga</v>
-      </c>
-      <c r="D80" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>5.5</v>
-      </c>
-      <c r="B81">
-        <v>2</v>
-      </c>
-      <c r="C81" t="str">
-        <v>Pruebas de aceptación (UAT con docentes)</v>
-      </c>
-      <c r="D81" t="str">
-        <v>5. Pruebas</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>5.6</v>
-      </c>
-      <c r="B82">
-        <v>2</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Corrección de defectos</v>
-      </c>
-      <c r="D82" t="str">
         <v>5. Pruebas</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D58"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/WBS_Tutor_Inteligente_ITM.xlsx
+++ b/data/WBS_Tutor_Inteligente_ITM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\itmentorsoft-wbs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E28A532-464A-457F-A14D-F4F66DA29F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7725C4C8-002C-43A9-909C-453B24D19D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -502,9 +502,6 @@
     <t>Regla del 100 %: los 5 entregables principales cubren todo el trabajo. Gestión del Proyecto agrupa dirección, cronograma, riesgos y monitoreo/cierre (proceso); la calidad del producto vive en la rama Pruebas.</t>
   </si>
   <si>
-    <t>2.1.3</t>
-  </si>
-  <si>
     <t>Tabla ADR</t>
   </si>
   <si>
@@ -515,6 +512,9 @@
   </si>
   <si>
     <t>Esquema de datos</t>
+  </si>
+  <si>
+    <t>2.3.1</t>
   </si>
 </sst>
 </file>
@@ -1480,44 +1480,44 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B32" s="10">
-        <v>3</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="A32" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="15">
+        <v>2</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="15" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B33" s="15">
         <v>2</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="15">
-        <v>2</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="A34" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" s="10">
+        <v>3</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1621,13 +1621,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B42" s="10">
         <v>3</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>75</v>
@@ -1649,13 +1649,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B44" s="10">
+        <v>3</v>
+      </c>
+      <c r="C44" s="11" t="s">
         <v>162</v>
-      </c>
-      <c r="B44" s="10">
-        <v>3</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>163</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>75</v>
